--- a/Assets/Level ideas.xlsx
+++ b/Assets/Level ideas.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Osama-App\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Documents\Unity\Matryoshka\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94721388-8624-425E-A6BA-537D63077576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9763D0-30F3-4556-82DA-2A2744AAE6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D7CD07F5-B6A9-4E1A-9152-6758E6D251FF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{D7CD07F5-B6A9-4E1A-9152-6758E6D251FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>Level</t>
   </si>
@@ -54,21 +53,6 @@
     <t>Movement around</t>
   </si>
   <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Move it</t>
-  </si>
-  <si>
-    <t>Move it around</t>
-  </si>
-  <si>
-    <t>Size matters</t>
-  </si>
-  <si>
-    <t>Up is not jump</t>
-  </si>
-  <si>
     <t>Jumping is one way/getting stuck and resetting</t>
   </si>
   <si>
@@ -78,13 +62,7 @@
     <t>Jumping to change parity</t>
   </si>
   <si>
-    <t>Is this the right way?</t>
-  </si>
-  <si>
     <t>Parity matters to pieces</t>
-  </si>
-  <si>
-    <t>Forgot my pants</t>
   </si>
   <si>
     <t>Multiple parity changes</t>
@@ -151,12 +129,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -171,8 +155,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,246 +492,224 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43240939-9CA8-490C-880F-4AC6927310CD}">
-  <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Level ideas.xlsx
+++ b/Assets/Level ideas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Documents\Unity\Matryoshka\Assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Osama-App\Documents\Unity Projects\Matryoshka Puzzle\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9763D0-30F3-4556-82DA-2A2744AAE6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8B47B7-C6ED-49CD-AE48-63113436C3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{D7CD07F5-B6A9-4E1A-9152-6758E6D251FF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D7CD07F5-B6A9-4E1A-9152-6758E6D251FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>Level</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Jumping</t>
   </si>
   <si>
-    <t>Movement forward</t>
-  </si>
-  <si>
     <t>Movement around</t>
   </si>
   <si>
@@ -62,9 +59,6 @@
     <t>Jumping to change parity</t>
   </si>
   <si>
-    <t>Parity matters to pieces</t>
-  </si>
-  <si>
     <t>Multiple parity changes</t>
   </si>
   <si>
@@ -114,6 +108,9 @@
   </si>
   <si>
     <t>Advanced levels from now on…</t>
+  </si>
+  <si>
+    <t>Size 3</t>
   </si>
 </sst>
 </file>
@@ -492,14 +489,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43240939-9CA8-490C-880F-4AC6927310CD}">
-  <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -515,201 +512,196 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Level ideas.xlsx
+++ b/Assets/Level ideas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Osama-App\Documents\Unity Projects\Matryoshka Puzzle\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8B47B7-C6ED-49CD-AE48-63113436C3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576A1F94-86FA-4455-8910-7F16AB937FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D7CD07F5-B6A9-4E1A-9152-6758E6D251FF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>Level</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>Testing general understanding</t>
-  </si>
-  <si>
-    <t>Blocked tiles</t>
   </si>
   <si>
     <t>Buttons to unlock blocked tiles</t>
@@ -489,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43240939-9CA8-490C-880F-4AC6927310CD}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" bestFit="1" customWidth="1"/>
@@ -557,7 +554,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -613,7 +610,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -621,7 +618,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -685,7 +682,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -693,15 +690,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Level ideas.xlsx
+++ b/Assets/Level ideas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Osama-App\Documents\Unity Projects\Matryoshka Puzzle\Assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Documents\Unity\Matryoshka\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576A1F94-86FA-4455-8910-7F16AB937FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DF7FB9-7CD2-4ADB-A17A-3A1A697E05A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D7CD07F5-B6A9-4E1A-9152-6758E6D251FF}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D7CD07F5-B6A9-4E1A-9152-6758E6D251FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -487,13 +487,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43240939-9CA8-490C-880F-4AC6927310CD}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -501,7 +501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -509,7 +509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -517,7 +517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -525,7 +525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -533,7 +533,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -541,7 +541,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -549,7 +549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -557,7 +557,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -565,23 +565,23 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -589,7 +589,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -597,7 +597,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -605,7 +605,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -613,7 +613,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -621,7 +621,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -629,7 +629,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -637,7 +637,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -645,7 +645,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -653,7 +653,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -661,7 +661,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -669,7 +669,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -677,7 +677,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -685,7 +685,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>

--- a/Assets/Level ideas.xlsx
+++ b/Assets/Level ideas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Documents\Unity\Matryoshka\Assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Osama-App\Documents\Unity Projects\Matryoshka Puzzle\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DF7FB9-7CD2-4ADB-A17A-3A1A697E05A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C156CC-BF0D-419F-931C-9EFD069BEBCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D7CD07F5-B6A9-4E1A-9152-6758E6D251FF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D7CD07F5-B6A9-4E1A-9152-6758E6D251FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>Level</t>
   </si>
@@ -71,15 +71,9 @@
     <t>Button size requirements</t>
   </si>
   <si>
-    <t>Button + jumping</t>
-  </si>
-  <si>
     <t>Size 3 buttons</t>
   </si>
   <si>
-    <t>Size 3 buttons + jumping</t>
-  </si>
-  <si>
     <t>Advanced level with buttons, jumping, and parity</t>
   </si>
   <si>
@@ -92,15 +86,6 @@
     <t>Teleporters do not change parity</t>
   </si>
   <si>
-    <t>Inactive teleporters + buttons</t>
-  </si>
-  <si>
-    <t>Multiple buttons</t>
-  </si>
-  <si>
-    <t>Multiple buttons with multiple size requirements</t>
-  </si>
-  <si>
     <t>Advanced level with teleporters, jumping, buttons, and parity</t>
   </si>
   <si>
@@ -108,6 +93,9 @@
   </si>
   <si>
     <t>Size 3</t>
+  </si>
+  <si>
+    <t>Multiple Teleporters</t>
   </si>
 </sst>
 </file>
@@ -486,14 +474,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43240939-9CA8-490C-880F-4AC6927310CD}">
-  <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -501,7 +489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -509,7 +497,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -517,7 +505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -525,7 +513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -533,7 +521,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -541,7 +529,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -549,15 +537,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -565,7 +553,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -573,7 +561,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -581,116 +569,76 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
